--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 46 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="P9" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>1</v>
+      <c r="R9" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V25" s="9" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V57" s="9" t="n">
         <v>3</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9897,11 +9897,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P95" s="9" t="n">
-        <v>3</v>
+      <c r="P95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10295,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="S99" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12625,8 +12625,8 @@
       <c r="S123" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
@@ -13514,7 +13514,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -13547,13 +13547,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -14009,7 +14009,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -14141,7 +14141,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14339,7 +14339,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 43 clubs short</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1376,8 +1376,8 @@
       <c r="T7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U7" s="9" t="n">
-        <v>0</v>
+      <c r="U7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V7" s="10" t="n">
         <v>4</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1749,8 +1749,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P11" s="9" t="n">
-        <v>1</v>
+      <c r="P11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>1</v>
@@ -1761,8 +1761,8 @@
       <c r="S11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2431,8 +2431,8 @@
       <c r="P18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>1</v>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="P20" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R20" s="9" t="n">
-        <v>0</v>
+      <c r="R20" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S20" s="9" t="n">
         <v>1</v>
@@ -3593,16 +3593,16 @@
         </is>
       </c>
       <c r="P30" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3692,8 +3692,8 @@
       <c r="P31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="9" t="n">
-        <v>1</v>
+      <c r="Q31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3883,8 +3883,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P33" s="9" t="n">
-        <v>3</v>
+      <c r="P33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="10" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4951,19 +4951,19 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R44" s="9" t="n">
-        <v>1</v>
+      <c r="R44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5465,8 +5465,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5838,8 +5838,8 @@
       <c r="T53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
+      <c r="U53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V53" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5935,8 +5935,8 @@
       <c r="T54" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U54" s="9" t="n">
-        <v>0</v>
+      <c r="U54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V54" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6599,8 +6599,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P61" s="9" t="n">
-        <v>3</v>
+      <c r="P61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8263,8 +8263,8 @@
       <c r="T78" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
+      <c r="U78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V78" s="9" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9803,8 +9803,8 @@
       <c r="P94" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q94" s="9" t="n">
-        <v>1</v>
+      <c r="Q94" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -13547,7 +13547,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -13580,7 +13580,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13613,13 +13613,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -13712,13 +13712,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -13778,7 +13778,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13811,7 +13811,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13844,7 +13844,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13910,7 +13910,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14042,13 +14042,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -14108,7 +14108,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -819,24 +819,24 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>28680967</v>
+        <v>28677777</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Ford Coimbatore Toastmaster Club</t>
+          <t>Centum Toastmasters Club</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>0</v>
@@ -894,14 +894,14 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X2" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -925,11 +925,11 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>28677777</v>
+        <v>28680692</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Centum Toastmasters Club</t>
+          <t>KG Toastmasters Club</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J3" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="K3" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -995,10 +995,10 @@
         <v>4</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X3" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -1022,15 +1022,15 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>28680692</v>
+        <v>28677445</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KG Toastmasters Club</t>
+          <t>Kovai Boschlers Toastmasters Club</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1070,29 +1070,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>0</v>
+      <c r="P4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1119,15 +1119,15 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>28677445</v>
+        <v>28678084</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Kovai Boschlers Toastmasters Club</t>
+          <t>Rappit Toastmasters Club</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1167,32 +1167,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P5" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="10" t="n">
-        <v>2</v>
+      <c r="P5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W5" s="10" t="n">
-        <v>5</v>
+      <c r="W5" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1216,15 +1216,15 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>28678084</v>
+        <v>4459223</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Rappit Toastmasters Club</t>
+          <t>Vitae Toastmasters Club</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1285,8 +1285,8 @@
       <c r="V6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W6" s="9" t="n">
-        <v>2</v>
+      <c r="W6" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>6</v>
@@ -1309,19 +1309,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4459223</v>
+        <v>5491781</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Vitae Toastmasters Club</t>
+          <t>Amrita Toastmasters Club</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1364,29 +1364,29 @@
       <c r="P7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="9" t="n">
-        <v>0</v>
+      <c r="Q7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="9" t="n">
-        <v>0</v>
+      <c r="S7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V7" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W7" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1410,15 +1410,15 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5491781</v>
+        <v>2148163</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Amrita Toastmasters Club</t>
+          <t>Coimbatore Toastmasters Club</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="10" t="n">
         <v>2</v>
@@ -1467,20 +1467,20 @@
       <c r="R8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="10" t="n">
-        <v>2</v>
+      <c r="S8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" s="10" t="n">
-        <v>3</v>
+      <c r="U8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V8" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1507,11 +1507,11 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2148163</v>
+        <v>28679231</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Coimbatore Toastmasters Club</t>
+          <t>Kovai Boschlers Toast &amp; Talk Club</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -1529,17 +1529,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
@@ -1555,20 +1555,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P9" s="9" t="n">
-        <v>2</v>
+      <c r="P9" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="Q9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>0</v>
+      <c r="R9" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="10" t="n">
-        <v>1</v>
+      <c r="T9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
@@ -1576,8 +1576,8 @@
       <c r="V9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W9" s="10" t="n">
-        <v>7</v>
+      <c r="W9" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1604,15 +1604,15 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>28679231</v>
+        <v>28679449</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Kovai Boschlers Toast &amp; Talk Club</t>
+          <t>Orion Spellbinders Toastmasters Club</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,17 +1626,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="P10" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>0</v>
@@ -1673,11 +1673,11 @@
       <c r="V10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>1</v>
+      <c r="W10" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1701,15 +1701,15 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>28679449</v>
+        <v>28680994</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Orion Spellbinders Toastmasters Club</t>
+          <t>TCS Maitree Coimbatore Toastmasters Club</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1749,8 +1749,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P11" s="10" t="n">
-        <v>8</v>
+      <c r="P11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>0</v>
@@ -1767,14 +1767,14 @@
       <c r="U11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W11" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="X11" s="10" t="n">
-        <v>6</v>
+      <c r="V11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -1794,15 +1794,15 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>28680994</v>
+        <v>28680449</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>TCS Maitree Coimbatore Toastmasters Club</t>
+          <t>Chettinad Toastmasters</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -1895,15 +1895,15 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>28680449</v>
+        <v>7432545</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Chettinad Toastmasters</t>
+          <t>HCL Pandyas</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1943,38 +1943,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P13" s="9" t="n">
-        <v>0</v>
+      <c r="P13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="9" t="n">
-        <v>0</v>
+      <c r="S13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X13" s="9" t="n">
-        <v>0</v>
+      <c r="X13" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -1992,11 +1992,11 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7432545</v>
+        <v>28680094</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>HCL Pandyas</t>
+          <t>KARUR TOASTMASTERS</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7</v>
+        <v>9</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2041,28 +2041,28 @@
         </is>
       </c>
       <c r="P14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>0</v>
+      <c r="W14" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2089,15 +2089,15 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>28680094</v>
+        <v>7517992</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>KARUR TOASTMASTERS</t>
+          <t>SIT Toastmasters Club III</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2111,17 +2111,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2137,17 +2137,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P15" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" s="10" t="n">
-        <v>2</v>
+      <c r="P15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="9" t="n">
         <v>0</v>
@@ -2155,11 +2155,11 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W15" s="10" t="n">
-        <v>5</v>
+      <c r="V15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2167,8 +2167,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="10" t="n">
-        <v>1</v>
+      <c r="Z15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2186,11 +2186,11 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>7517992</v>
+        <v>28677230</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>SIT Toastmasters Club III</t>
+          <t>SIT Toastmasters Club IV</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" s="9" t="n">
         <v>0</v>
@@ -2258,8 +2258,8 @@
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X16" s="10" t="n">
-        <v>7</v>
+      <c r="X16" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -2283,15 +2283,15 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28677230</v>
+        <v>28677188</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>SIT Toastmasters Club IV</t>
+          <t>Toastmasters Club of Madurai</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2349,20 +2349,20 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>0</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="X17" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2380,15 +2380,15 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>28677188</v>
+        <v>4413695</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Madurai</t>
+          <t>Virudhunagar Toastmasters Club</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2446,20 +2446,20 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="10" t="n">
-        <v>4</v>
+      <c r="V18" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X18" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="10" t="n">
-        <v>1</v>
+      <c r="Z18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2473,19 +2473,19 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4413695</v>
+        <v>7809216</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Virudhunagar Toastmasters Club</t>
+          <t>Award City Toastmasters Club</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2528,35 +2528,35 @@
       <c r="P19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="9" t="n">
-        <v>0</v>
+      <c r="Q19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
+      <c r="S19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X19" s="9" t="n">
-        <v>2</v>
+      <c r="X19" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2574,11 +2574,11 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7809216</v>
+        <v>28677879</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Award City Toastmasters Club</t>
+          <t>Dindigul Toastmasters Club</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -2596,17 +2596,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M20" s="7" t="n">
@@ -2622,8 +2622,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P20" s="9" t="n">
-        <v>0</v>
+      <c r="P20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q20" s="10" t="n">
         <v>2</v>
@@ -2631,8 +2631,8 @@
       <c r="R20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="10" t="n">
-        <v>2</v>
+      <c r="S20" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T20" s="10" t="n">
         <v>1</v>
@@ -2647,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="9" t="n">
         <v>0</v>
@@ -2671,15 +2671,15 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>28677879</v>
+        <v>7786341</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Dindigul Toastmasters Club</t>
+          <t>PSNA Toastmasters Club</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
@@ -2719,23 +2719,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P21" s="10" t="n">
-        <v>4</v>
+      <c r="P21" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q21" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="10" t="n">
-        <v>1</v>
+      <c r="T21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
@@ -2768,15 +2768,15 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>7786341</v>
+        <v>5511091</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>PSNA Toastmasters Club</t>
+          <t>SIT Toastmaster Club - 1</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2804,11 +2804,11 @@
         </is>
       </c>
       <c r="M22" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr">
@@ -2816,41 +2816,41 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P22" s="9" t="n">
-        <v>3</v>
+      <c r="P22" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Q22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R22" s="9" t="n">
-        <v>1</v>
+      <c r="R22" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="10" t="n">
-        <v>4</v>
+      <c r="X22" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="10" t="n">
-        <v>1</v>
+      <c r="Z22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2865,11 +2865,11 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5511091</v>
+        <v>5511707</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>SIT Toastmaster Club - 1</t>
+          <t>SIT Toastmaster Club - 2</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -2901,11 +2901,11 @@
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr">
@@ -2913,23 +2913,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P23" s="10" t="n">
-        <v>6</v>
+      <c r="P23" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q23" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S23" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="X23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -2946,8 +2946,8 @@
       <c r="Z23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" s="9" t="n">
-        <v>0</v>
+      <c r="AA23" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2962,15 +2962,15 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5511707</v>
+        <v>3270615</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>SIT Toastmaster Club - 2</t>
+          <t>Trichy Toastmasters Club</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="S24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>3</v>
+      <c r="X24" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3050,24 +3050,24 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3270615</v>
+        <v>28679724</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Trichy Toastmasters Club</t>
+          <t>Karpagam Tech Toastmasters Club</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-22</v>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M25" s="7" t="n">
@@ -3107,11 +3107,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>0</v>
+      <c r="P25" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
@@ -3125,14 +3125,14 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W25" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3156,15 +3156,15 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>28679724</v>
+        <v>7225106</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Karpagam Tech Toastmasters Club</t>
+          <t>SLB Coimbatore Toastmasters Club</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3204,8 +3204,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P26" s="10" t="n">
-        <v>5</v>
+      <c r="P26" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q26" s="10" t="n">
         <v>2</v>
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="9" t="n">
         <v>0</v>
@@ -3225,8 +3225,8 @@
       <c r="V26" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W26" s="10" t="n">
-        <v>6</v>
+      <c r="W26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3253,15 +3253,15 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7225106</v>
+        <v>7944329</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>SLB Coimbatore Toastmasters Club</t>
+          <t>VCEW Toastmasters Club</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3301,32 +3301,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="10" t="n">
-        <v>4</v>
+      <c r="V27" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3350,11 +3350,11 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7944329</v>
+        <v>28677389</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>VCEW Toastmasters Club</t>
+          <t>Western Ghats Coimbatore Toastmasters Club</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M28" s="7" t="n">
@@ -3398,32 +3398,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P28" s="10" t="n">
-        <v>5</v>
+      <c r="P28" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="10" t="n">
+      <c r="R28" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>0</v>
+      <c r="S28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
@@ -3443,19 +3443,19 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>28677389</v>
+        <v>28679730</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Western Ghats Coimbatore Toastmasters Club</t>
+          <t>Karpagam College of Engineering Toastmasters</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3496,16 +3496,16 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T29" s="9" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -3544,11 +3544,11 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>28679730</v>
+        <v>7934411</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Karpagam College of Engineering Toastmasters</t>
+          <t>Lauritz Knudsen Coimbatore Toastmasters Club</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -3569,10 +3569,10 @@
         <v>16</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -3601,8 +3601,8 @@
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>0</v>
+      <c r="S30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>0</v>
@@ -3610,11 +3610,11 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="10" t="n">
-        <v>4</v>
+      <c r="V30" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>7</v>
@@ -3641,39 +3641,39 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7934411</v>
+        <v>6938059</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Lauritz Knudsen Coimbatore Toastmasters Club</t>
+          <t>Sri Eshwar Toastmasters Club</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
@@ -3689,29 +3689,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="10" t="n">
+      <c r="P31" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
+      <c r="R31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W31" s="9" t="n">
-        <v>0</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>7</v>
@@ -3738,11 +3738,11 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6938059</v>
+        <v>28678844</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Sri Eshwar Toastmasters Club</t>
+          <t>Sri Eshwar Toastmasters Club - Chapter 2</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>2</v>
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="P32" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32" s="9" t="n">
         <v>1</v>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>7</v>
@@ -3831,19 +3831,19 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>28678844</v>
+        <v>4469699</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Sri Eshwar Toastmasters Club - Chapter 2</t>
+          <t>Coimbatore Speakers Forum</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3883,20 +3883,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P33" s="10" t="n">
-        <v>6</v>
+      <c r="P33" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q33" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R33" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" s="10" t="n">
-        <v>1</v>
+      <c r="R33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U33" s="9" t="n">
         <v>0</v>
@@ -3932,15 +3932,15 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4469699</v>
+        <v>28680967</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Coimbatore Speakers Forum</t>
+          <t>Ford Coimbatore Toastmaster Club</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="10" t="n">
-        <v>2</v>
+      <c r="S34" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -3998,14 +3998,14 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W34" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X34" s="10" t="n">
-        <v>7</v>
+      <c r="V34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y34" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-25</v>
+        <v>-8</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>6</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5215,17 +5215,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="9" t="n">
         <v>0</v>
@@ -5259,11 +5259,11 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="9" t="n">
-        <v>0</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>6</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-24</v>
+        <v>-19</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5841,11 +5841,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>0</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>7</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10288,8 +10288,8 @@
       <c r="P99" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" s="9" t="n">
-        <v>1</v>
+      <c r="Q99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10303,8 +10303,8 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>2</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -14020,7 +14020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14084,25 +14084,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -14111,7 +14111,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -14122,29 +14122,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -14155,29 +14155,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -14188,62 +14188,62 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.86</v>
+        <v>3.83</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3.83</v>
+        <v>4.5</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -14254,20 +14254,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -14276,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -14287,29 +14287,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -14330,16 +14330,16 @@
         <v>2.17</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -14348,31 +14348,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -14386,14 +14386,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -14405,10 +14405,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -14419,20 +14419,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -14441,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14452,21 +14452,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
@@ -14474,18 +14474,18 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -14518,29 +14518,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14551,29 +14551,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14584,14 +14584,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -14606,31 +14606,31 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -14650,29 +14650,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="n">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>3</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -14683,17 +14683,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -14702,10 +14702,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -14716,29 +14716,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14749,59 +14749,59 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="D22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>3</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -14815,20 +14815,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -14848,20 +14848,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -14881,14 +14881,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -14903,7 +14903,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -14914,20 +14914,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -14947,66 +14947,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/230/inyear.xlsx
+++ b/docs/d/230/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="P20" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="10" t="n">
         <v>2</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="10" t="n">
         <v>1</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>4</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4957,16 +4957,16 @@
         <v>2</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U44" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V44" s="9" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5241,8 +5241,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P47" s="9" t="n">
-        <v>3</v>
+      <c r="P47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5250,8 +5250,8 @@
       <c r="R47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S47" s="9" t="n">
-        <v>1</v>
+      <c r="S47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T47" s="9" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6708,8 +6708,8 @@
       <c r="S62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
+      <c r="T62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>1</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q90" s="10" t="n">
         <v>2</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -9919,7 +9919,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>5</v>
@@ -10098,7 +10098,7 @@
         <v>2</v>
       </c>
       <c r="R97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S97" s="10" t="n">
         <v>2</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>1</v>
@@ -14327,13 +14327,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -14360,7 +14360,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -14459,7 +14459,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -14705,7 +14705,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
